--- a/adventureworks_report.xlsx
+++ b/adventureworks_report.xlsx
@@ -458,254 +458,232 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
+      <c r="A2" t="n">
+        <v>2022</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2011-05</t>
+          <t>2022-05</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D2" t="n">
-        <v>567020.95</v>
+        <v>582415.28</v>
       </c>
       <c r="E2" t="n">
-        <v>13186.53</v>
+        <v>12391.81</v>
       </c>
       <c r="F2" t="n">
-        <v>1929641.5</v>
+        <v>1993355.26</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
+      <c r="A3" t="n">
+        <v>2022</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2011-06</t>
+          <t>2022-06</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>141</v>
+        <v>217</v>
       </c>
       <c r="D3" t="n">
-        <v>507096.47</v>
+        <v>2244313.14</v>
       </c>
       <c r="E3" t="n">
-        <v>3596.43</v>
+        <v>10342.46</v>
       </c>
       <c r="F3" t="n">
-        <v>2000609.36</v>
+        <v>2060879.13</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
+      <c r="A4" t="n">
+        <v>2022</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2011-07</t>
+          <t>2022-07</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="D4" t="n">
-        <v>2292182.88</v>
+        <v>1868508.36</v>
       </c>
       <c r="E4" t="n">
-        <v>9922.870000000001</v>
+        <v>8690.74</v>
       </c>
       <c r="F4" t="n">
-        <v>2071577.23</v>
+        <v>2128403.01</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
+      <c r="A5" t="n">
+        <v>2022</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2011-08</t>
+          <t>2022-08</t>
         </is>
       </c>
       <c r="C5" t="n">
+        <v>189</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1483277.04</v>
+      </c>
+      <c r="E5" t="n">
+        <v>7848.03</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2195926.89</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2022-09</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
         <v>250</v>
       </c>
-      <c r="D5" t="n">
-        <v>2800576.17</v>
-      </c>
-      <c r="E5" t="n">
-        <v>11202.3</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2142545.09</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2011-09</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>157</v>
-      </c>
       <c r="D6" t="n">
-        <v>554791.61</v>
+        <v>3183714.32</v>
       </c>
       <c r="E6" t="n">
-        <v>3533.7</v>
+        <v>12734.86</v>
       </c>
       <c r="F6" t="n">
-        <v>2213512.96</v>
+        <v>2263450.77</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
+      <c r="A7" t="n">
+        <v>2022</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2011-10</t>
+          <t>2022-10</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>327</v>
+        <v>239</v>
       </c>
       <c r="D7" t="n">
-        <v>5156269.53</v>
+        <v>2543935.27</v>
       </c>
       <c r="E7" t="n">
-        <v>15768.41</v>
+        <v>10644.08</v>
       </c>
       <c r="F7" t="n">
-        <v>2284480.82</v>
+        <v>2330974.65</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
+      <c r="A8" t="n">
+        <v>2022</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2011-11</t>
+          <t>2022-11</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>230</v>
+        <v>267</v>
       </c>
       <c r="D8" t="n">
-        <v>815313.02</v>
+        <v>1603313.51</v>
       </c>
       <c r="E8" t="n">
-        <v>3544.84</v>
+        <v>6004.92</v>
       </c>
       <c r="F8" t="n">
-        <v>2355448.69</v>
+        <v>2398498.53</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
+      <c r="A9" t="n">
+        <v>2022</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2011-12</t>
+          <t>2022-12</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>228</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>1462448.9</v>
+        <v>2807217.25</v>
       </c>
       <c r="E9" t="n">
-        <v>6414.25</v>
+        <v>10474.69</v>
       </c>
       <c r="F9" t="n">
-        <v>2426416.55</v>
+        <v>2466022.4</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
+      <c r="A10" t="n">
+        <v>2023</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2012-01</t>
+          <t>2023-01</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>336</v>
+        <v>259</v>
       </c>
       <c r="D10" t="n">
-        <v>4458337.44</v>
+        <v>2325568.6</v>
       </c>
       <c r="E10" t="n">
-        <v>13268.86</v>
+        <v>8979.030000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>2497384.42</v>
+        <v>2533546.28</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
+      <c r="A11" t="n">
+        <v>2023</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2012-02</t>
+          <t>2023-02</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="D11" t="n">
-        <v>1649051.9</v>
+        <v>1620826.1</v>
       </c>
       <c r="E11" t="n">
-        <v>7529.92</v>
+        <v>7681.64</v>
       </c>
       <c r="F11" t="n">
-        <v>2568352.28</v>
+        <v>2601070.16</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
+      <c r="A12" t="n">
+        <v>2023</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2012-03</t>
+          <t>2023-03</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -718,18 +696,16 @@
         <v>10974.83</v>
       </c>
       <c r="F12" t="n">
-        <v>2639320.15</v>
+        <v>2668594.04</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
+      <c r="A13" t="n">
+        <v>2023</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2012-04</t>
+          <t>2023-04</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -742,18 +718,16 @@
         <v>6958.82</v>
       </c>
       <c r="F13" t="n">
-        <v>2710288.01</v>
+        <v>2736117.92</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
+      <c r="A14" t="n">
+        <v>2023</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2012-05</t>
+          <t>2023-05</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -766,18 +740,16 @@
         <v>11784.73</v>
       </c>
       <c r="F14" t="n">
-        <v>2781255.88</v>
+        <v>2803641.8</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
+      <c r="A15" t="n">
+        <v>2023</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2012-06</t>
+          <t>2023-06</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -790,18 +762,16 @@
         <v>11822.17</v>
       </c>
       <c r="F15" t="n">
-        <v>2852223.74</v>
+        <v>2871165.67</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
+      <c r="A16" t="n">
+        <v>2023</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2012-07</t>
+          <t>2023-07</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -814,18 +784,16 @@
         <v>9974.629999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>2923191.61</v>
+        <v>2938689.55</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
+      <c r="A17" t="n">
+        <v>2023</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2012-08</t>
+          <t>2023-08</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -838,18 +806,16 @@
         <v>8570</v>
       </c>
       <c r="F17" t="n">
-        <v>2994159.47</v>
+        <v>3006213.43</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
+      <c r="A18" t="n">
+        <v>2023</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2012-09</t>
+          <t>2023-09</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -862,18 +828,16 @@
         <v>11027.63</v>
       </c>
       <c r="F18" t="n">
-        <v>3065127.34</v>
+        <v>3073737.31</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
+      <c r="A19" t="n">
+        <v>2023</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2012-10</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -886,18 +850,16 @@
         <v>8903.610000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>3136095.21</v>
+        <v>3141261.19</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
+      <c r="A20" t="n">
+        <v>2023</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2012-11</t>
+          <t>2023-11</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -910,18 +872,16 @@
         <v>5475.6</v>
       </c>
       <c r="F20" t="n">
-        <v>3207063.07</v>
+        <v>3208785.06</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
+      <c r="A21" t="n">
+        <v>2023</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2012-12</t>
+          <t>2023-12</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -934,18 +894,16 @@
         <v>8404.360000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>3278030.94</v>
+        <v>3276308.94</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
+      <c r="A22" t="n">
+        <v>2024</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2013-01</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -958,415 +916,381 @@
         <v>5850.15</v>
       </c>
       <c r="F22" t="n">
-        <v>3348998.8</v>
+        <v>3343832.82</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
+      <c r="A23" t="n">
+        <v>2024</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2013-02</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="D23" t="n">
-        <v>2600218.87</v>
+        <v>2629322.45</v>
       </c>
       <c r="E23" t="n">
-        <v>8000.67</v>
+        <v>7779.06</v>
       </c>
       <c r="F23" t="n">
-        <v>3419966.67</v>
+        <v>3411356.7</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
+      <c r="A24" t="n">
+        <v>2024</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2013-03</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D24" t="n">
-        <v>3831605.94</v>
+        <v>3826046.07</v>
       </c>
       <c r="E24" t="n">
-        <v>8688.450000000001</v>
+        <v>8636.67</v>
       </c>
       <c r="F24" t="n">
-        <v>3490934.53</v>
+        <v>3478880.58</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
+      <c r="A25" t="n">
+        <v>2024</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2013-04</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D25" t="n">
-        <v>2840711.17</v>
+        <v>2841585.78</v>
       </c>
       <c r="E25" t="n">
-        <v>6637.18</v>
+        <v>6670.39</v>
       </c>
       <c r="F25" t="n">
-        <v>3561902.4</v>
+        <v>3546404.46</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
+      <c r="A26" t="n">
+        <v>2024</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2013-05</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="D26" t="n">
-        <v>3658084.95</v>
+        <v>3672137.65</v>
       </c>
       <c r="E26" t="n">
-        <v>8546.93</v>
+        <v>8422.33</v>
       </c>
       <c r="F26" t="n">
-        <v>3632870.26</v>
+        <v>3613928.33</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
+      <c r="A27" t="n">
+        <v>2024</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2013-06</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>719</v>
+        <v>741</v>
       </c>
       <c r="D27" t="n">
-        <v>5726265.26</v>
+        <v>5707181.09</v>
       </c>
       <c r="E27" t="n">
-        <v>7964.21</v>
+        <v>7702</v>
       </c>
       <c r="F27" t="n">
-        <v>3703838.13</v>
+        <v>3681452.21</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
+      <c r="A28" t="n">
+        <v>2024</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2013-07</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1740</v>
+        <v>1755</v>
       </c>
       <c r="D28" t="n">
-        <v>5521840.84</v>
+        <v>5546401.07</v>
       </c>
       <c r="E28" t="n">
-        <v>3173.47</v>
+        <v>3160.34</v>
       </c>
       <c r="F28" t="n">
-        <v>3774805.99</v>
+        <v>3748976.09</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
+      <c r="A29" t="n">
+        <v>2024</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2013-08</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1789</v>
+        <v>1785</v>
       </c>
       <c r="D29" t="n">
-        <v>3733973</v>
+        <v>3724394.9</v>
       </c>
       <c r="E29" t="n">
-        <v>2087.18</v>
+        <v>2086.5</v>
       </c>
       <c r="F29" t="n">
-        <v>3845773.86</v>
+        <v>3816499.97</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
+      <c r="A30" t="n">
+        <v>2024</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2013-09</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1791</v>
+        <v>1796</v>
       </c>
       <c r="D30" t="n">
-        <v>5083505.34</v>
+        <v>5091152.26</v>
       </c>
       <c r="E30" t="n">
-        <v>2838.36</v>
+        <v>2834.72</v>
       </c>
       <c r="F30" t="n">
-        <v>3916741.72</v>
+        <v>3884023.85</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
+      <c r="A31" t="n">
+        <v>2024</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2013-10</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1968</v>
+        <v>1971</v>
       </c>
       <c r="D31" t="n">
-        <v>5374375.94</v>
+        <v>5401903.75</v>
       </c>
       <c r="E31" t="n">
-        <v>2730.88</v>
+        <v>2740.69</v>
       </c>
       <c r="F31" t="n">
-        <v>3987709.59</v>
+        <v>3951547.72</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
+      <c r="A32" t="n">
+        <v>2024</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2013-11</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2103</v>
+        <v>2100</v>
       </c>
       <c r="D32" t="n">
-        <v>3694668</v>
+        <v>3671582.38</v>
       </c>
       <c r="E32" t="n">
-        <v>1756.86</v>
+        <v>1748.37</v>
       </c>
       <c r="F32" t="n">
-        <v>4058677.45</v>
+        <v>4019071.6</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
+      <c r="A33" t="n">
+        <v>2024</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2013-12</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2050</v>
+        <v>2053</v>
       </c>
       <c r="D33" t="n">
-        <v>4560577.1</v>
+        <v>4568717.58</v>
       </c>
       <c r="E33" t="n">
-        <v>2224.67</v>
+        <v>2225.39</v>
       </c>
       <c r="F33" t="n">
-        <v>4129645.32</v>
+        <v>4086595.48</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
+      <c r="A34" t="n">
+        <v>2025</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2014-01</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2141</v>
+        <v>2136</v>
       </c>
       <c r="D34" t="n">
-        <v>4798027.87</v>
+        <v>4783231.67</v>
       </c>
       <c r="E34" t="n">
-        <v>2241.02</v>
+        <v>2239.34</v>
       </c>
       <c r="F34" t="n">
-        <v>4200613.18</v>
+        <v>4154119.36</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
+      <c r="A35" t="n">
+        <v>2025</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2014-02</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1756</v>
+        <v>1857</v>
       </c>
       <c r="D35" t="n">
-        <v>1478213.29</v>
+        <v>3987943.62</v>
       </c>
       <c r="E35" t="n">
-        <v>841.8099999999999</v>
+        <v>2147.52</v>
       </c>
       <c r="F35" t="n">
-        <v>4271581.05</v>
+        <v>4221643.24</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
+      <c r="A36" t="n">
+        <v>2025</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2014-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2399</v>
+        <v>2304</v>
       </c>
       <c r="D36" t="n">
-        <v>8097036.31</v>
+        <v>5585675.81</v>
       </c>
       <c r="E36" t="n">
-        <v>3375.17</v>
+        <v>2424.34</v>
       </c>
       <c r="F36" t="n">
-        <v>4342548.91</v>
+        <v>4289167.12</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
+      <c r="A37" t="n">
+        <v>2025</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2014-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2115</v>
+        <v>2279</v>
       </c>
       <c r="D37" t="n">
-        <v>1985886.15</v>
+        <v>5847164.69</v>
       </c>
       <c r="E37" t="n">
-        <v>938.95</v>
+        <v>2565.67</v>
       </c>
       <c r="F37" t="n">
-        <v>4413516.78</v>
+        <v>4356690.99</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
+      <c r="A38" t="n">
+        <v>2025</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2014-05</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2411</v>
+        <v>2218</v>
       </c>
       <c r="D38" t="n">
-        <v>6006183.21</v>
+        <v>2108405.79</v>
       </c>
       <c r="E38" t="n">
-        <v>2491.16</v>
+        <v>950.59</v>
       </c>
       <c r="F38" t="n">
-        <v>4484484.64</v>
+        <v>4424214.87</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
+      <c r="A39" t="n">
+        <v>2025</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2014-06</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>939</v>
+        <v>905</v>
       </c>
       <c r="D39" t="n">
-        <v>54151.48</v>
+        <v>52478.19</v>
       </c>
       <c r="E39" t="n">
-        <v>57.67</v>
+        <v>57.99</v>
       </c>
       <c r="F39" t="n">
-        <v>4555452.51</v>
+        <v>4491738.75</v>
       </c>
     </row>
   </sheetData>
@@ -1408,7 +1332,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2011-04</t>
+          <t>2022-04</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -1424,7 +1348,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2011-12</t>
+          <t>2022-12</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1440,7 +1364,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2012-01</t>
+          <t>2023-01</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1456,7 +1380,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2012-02</t>
+          <t>2023-02</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1472,7 +1396,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2012-03</t>
+          <t>2023-03</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1488,7 +1412,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2012-04</t>
+          <t>2023-04</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1504,7 +1428,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2012-05</t>
+          <t>2023-05</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1520,7 +1444,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2012-06</t>
+          <t>2023-06</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1536,7 +1460,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2012-07</t>
+          <t>2023-07</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1552,7 +1476,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2012-08</t>
+          <t>2023-08</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1568,7 +1492,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2012-09</t>
+          <t>2023-09</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1584,7 +1508,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2012-10</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1600,7 +1524,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2013-02</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1616,7 +1540,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2013-04</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1632,7 +1556,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2013-05</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1648,7 +1572,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2013-06</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1664,7 +1588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2013-07</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1680,39 +1604,39 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2013-08</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="C19" t="n">
-        <v>5696578.01</v>
+        <v>5828672.51</v>
       </c>
       <c r="D19" t="n">
-        <v>16754.64</v>
+        <v>16372.68</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2013-09</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="C20" t="n">
-        <v>3846599.88</v>
+        <v>3714505.38</v>
       </c>
       <c r="D20" t="n">
-        <v>16027.5</v>
+        <v>16582.61</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2013-10</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1728,7 +1652,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2013-11</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1744,151 +1668,151 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2013-12</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>272</v>
+        <v>288</v>
       </c>
       <c r="C23" t="n">
-        <v>4878800.9</v>
+        <v>5155499.09</v>
       </c>
       <c r="D23" t="n">
-        <v>17936.77</v>
+        <v>17901.04</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2014-01</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>278</v>
+        <v>262</v>
       </c>
       <c r="C24" t="n">
-        <v>4602426.98</v>
+        <v>4325728.78</v>
       </c>
       <c r="D24" t="n">
-        <v>16555.49</v>
+        <v>16510.42</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2014-02</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>293</v>
+        <v>310</v>
       </c>
       <c r="C25" t="n">
-        <v>5002602.77</v>
+        <v>5880015.97</v>
       </c>
       <c r="D25" t="n">
-        <v>17073.73</v>
+        <v>18967.79</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2014-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>309</v>
+        <v>292</v>
       </c>
       <c r="C26" t="n">
-        <v>5974363.78</v>
+        <v>5096950.59</v>
       </c>
       <c r="D26" t="n">
-        <v>19334.51</v>
+        <v>17455.31</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2014-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>337</v>
+        <v>353</v>
       </c>
       <c r="C27" t="n">
-        <v>6067960.03</v>
+        <v>6327446.82</v>
       </c>
       <c r="D27" t="n">
-        <v>18005.82</v>
+        <v>17924.78</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2014-05</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>349</v>
+        <v>333</v>
       </c>
       <c r="C28" t="n">
-        <v>6113171.9</v>
+        <v>5853685.11</v>
       </c>
       <c r="D28" t="n">
-        <v>17516.25</v>
+        <v>17578.63</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2014-06</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>378</v>
+        <v>394</v>
       </c>
       <c r="C29" t="n">
-        <v>7399101.19</v>
+        <v>7764024.84</v>
       </c>
       <c r="D29" t="n">
-        <v>19574.34</v>
+        <v>19705.65</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2014-07</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>432</v>
       </c>
       <c r="C30" t="n">
-        <v>7541613.36</v>
+        <v>7421257.98</v>
       </c>
       <c r="D30" t="n">
-        <v>17457.44</v>
+        <v>17178.84</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2014-08</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="C31" t="n">
-        <v>821182.59</v>
+        <v>576614.3199999999</v>
       </c>
       <c r="D31" t="n">
-        <v>17107.97</v>
+        <v>18019.2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2014-09</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -2084,16 +2008,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C2" t="n">
-        <v>7.81</v>
+        <v>7.76</v>
       </c>
       <c r="D2" t="n">
-        <v>435937.01</v>
+        <v>432585.76</v>
       </c>
       <c r="E2" t="n">
-        <v>59045.57</v>
+        <v>58864.84</v>
       </c>
     </row>
     <row r="3">
@@ -2103,13 +2027,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18664</v>
+        <v>18663</v>
       </c>
       <c r="C3" t="n">
         <v>1.48</v>
       </c>
       <c r="D3" t="n">
-        <v>1859.69</v>
+        <v>1859.41</v>
       </c>
       <c r="E3" t="n">
         <v>1030.98</v>
@@ -2122,16 +2046,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C4" t="n">
-        <v>8.699999999999999</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>75793.14999999999</v>
+        <v>74873.75</v>
       </c>
       <c r="E4" t="n">
-        <v>13064.91</v>
+        <v>12813.74</v>
       </c>
     </row>
   </sheetData>
@@ -3116,7 +3040,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Information Services</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3131,7 +3055,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Information Services</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3191,12 +3115,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Human Resources</t>
+          <t>Quality Assurance</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Executive General and Administration</t>
+          <t>Quality Assurance</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -3206,12 +3130,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Production Control</t>
+          <t>Human Resources</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>Executive General and Administration</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -3221,12 +3145,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Quality Assurance</t>
+          <t>Production Control</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Quality Assurance</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="C12" t="n">
